--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4842242F-D130-4AD9-9D36-15D5E930C389}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17E37448-4081-435B-9D75-A90A063593FC}"/>
   </bookViews>
@@ -715,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -723,6 +723,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1248,7 +1260,7 @@
       <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="7">
         <v>1</v>
       </c>
       <c r="E20" s="2"/>
@@ -1272,7 +1284,7 @@
       <c r="C21" t="s">
         <v>27</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="7">
         <v>1</v>
       </c>
       <c r="F21" s="2"/>
@@ -1290,7 +1302,7 @@
       <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="7">
         <v>2</v>
       </c>
       <c r="F22" s="2"/>
@@ -1308,7 +1320,7 @@
       <c r="C23" t="s">
         <v>27</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="7">
         <v>3</v>
       </c>
       <c r="F23" s="2"/>
@@ -1326,7 +1338,7 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="7">
         <v>1</v>
       </c>
       <c r="F24" s="2"/>
@@ -1344,7 +1356,7 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="7">
         <v>2</v>
       </c>
       <c r="F25" s="2"/>
@@ -1362,7 +1374,7 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="7">
         <v>3</v>
       </c>
       <c r="F26" s="2"/>
@@ -1380,7 +1392,7 @@
       <c r="C27" t="s">
         <v>27</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="7">
         <v>1</v>
       </c>
       <c r="F27" s="2"/>
@@ -1398,7 +1410,7 @@
       <c r="C28" t="s">
         <v>27</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="7">
         <v>2</v>
       </c>
       <c r="F28" s="2"/>
@@ -1416,7 +1428,7 @@
       <c r="C29" t="s">
         <v>27</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="7">
         <v>3</v>
       </c>
       <c r="F29" s="2"/>
@@ -1434,7 +1446,7 @@
       <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="7">
         <v>1</v>
       </c>
       <c r="F30" s="2"/>
@@ -1452,7 +1464,7 @@
       <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="7">
         <v>2</v>
       </c>
       <c r="F31" s="2"/>
@@ -1470,7 +1482,7 @@
       <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="7">
         <v>3</v>
       </c>
       <c r="F32" s="2"/>
@@ -1478,10 +1490,14 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+    </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="D34" s="7"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1493,7 +1509,7 @@
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1531,7 +1547,7 @@
       <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="7">
         <v>1</v>
       </c>
       <c r="E36" s="2"/>
@@ -1555,7 +1571,7 @@
       <c r="C37" t="s">
         <v>27</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="7">
         <v>1</v>
       </c>
       <c r="F37" s="2"/>
@@ -1573,7 +1589,7 @@
       <c r="C38" t="s">
         <v>27</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="7">
         <v>2</v>
       </c>
       <c r="F38" s="2"/>
@@ -1591,7 +1607,7 @@
       <c r="C39" t="s">
         <v>27</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="7">
         <v>3</v>
       </c>
       <c r="F39" s="2"/>
@@ -1609,7 +1625,7 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="7">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
@@ -1627,7 +1643,7 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="7">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
@@ -1645,7 +1661,7 @@
       <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="7">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
@@ -1663,7 +1679,7 @@
       <c r="C43" t="s">
         <v>27</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="7">
         <v>1</v>
       </c>
       <c r="F43" s="2"/>
@@ -1681,7 +1697,7 @@
       <c r="C44" t="s">
         <v>27</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="7">
         <v>2</v>
       </c>
       <c r="F44" s="2"/>
@@ -1699,7 +1715,7 @@
       <c r="C45" t="s">
         <v>27</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="7">
         <v>3</v>
       </c>
       <c r="F45" s="2"/>
@@ -1717,7 +1733,7 @@
       <c r="C46" t="s">
         <v>15</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="7">
         <v>1</v>
       </c>
       <c r="F46" s="2"/>
@@ -1735,7 +1751,7 @@
       <c r="C47" t="s">
         <v>15</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="7">
         <v>2</v>
       </c>
       <c r="F47" s="2"/>
@@ -1753,7 +1769,7 @@
       <c r="C48" t="s">
         <v>15</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="7">
         <v>3</v>
       </c>
       <c r="F48" s="2"/>
@@ -1761,10 +1777,14 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
     </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D49" s="7"/>
+    </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -1776,7 +1796,7 @@
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1814,7 +1834,7 @@
       <c r="C52" t="s">
         <v>14</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="7">
         <v>1</v>
       </c>
       <c r="E52" s="2"/>
@@ -1838,7 +1858,7 @@
       <c r="C53" t="s">
         <v>27</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="7">
         <v>1</v>
       </c>
       <c r="F53" s="2"/>
@@ -1856,7 +1876,7 @@
       <c r="C54" t="s">
         <v>27</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="7">
         <v>2</v>
       </c>
       <c r="F54" s="2"/>
@@ -1874,7 +1894,7 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="7">
         <v>3</v>
       </c>
       <c r="F55" s="2"/>
@@ -1892,7 +1912,7 @@
       <c r="C56" t="s">
         <v>15</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="7">
         <v>1</v>
       </c>
       <c r="F56" s="2"/>
@@ -1910,7 +1930,7 @@
       <c r="C57" t="s">
         <v>15</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="7">
         <v>2</v>
       </c>
       <c r="F57" s="2"/>
@@ -1928,7 +1948,7 @@
       <c r="C58" t="s">
         <v>15</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="7">
         <v>3</v>
       </c>
       <c r="F58" s="2"/>
@@ -1946,7 +1966,7 @@
       <c r="C59" t="s">
         <v>27</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="7">
         <v>1</v>
       </c>
       <c r="F59" s="2"/>
@@ -1964,7 +1984,7 @@
       <c r="C60" t="s">
         <v>27</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="7">
         <v>2</v>
       </c>
       <c r="F60" s="2"/>
@@ -1982,7 +2002,7 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="7">
         <v>3</v>
       </c>
       <c r="F61" s="2"/>
@@ -2000,7 +2020,7 @@
       <c r="C62" t="s">
         <v>15</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="7">
         <v>1</v>
       </c>
       <c r="F62" s="2"/>
@@ -2018,7 +2038,7 @@
       <c r="C63" t="s">
         <v>15</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="7">
         <v>2</v>
       </c>
       <c r="F63" s="2"/>
@@ -2036,7 +2056,7 @@
       <c r="C64" t="s">
         <v>15</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="7">
         <v>3</v>
       </c>
       <c r="F64" s="2"/>
@@ -2044,10 +2064,14 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D65" s="7"/>
+    </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
@@ -2059,7 +2083,7 @@
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2097,7 +2121,7 @@
       <c r="C68" t="s">
         <v>14</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="7">
         <v>1</v>
       </c>
       <c r="E68" s="2"/>
@@ -2121,7 +2145,7 @@
       <c r="C69" t="s">
         <v>27</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="7">
         <v>1</v>
       </c>
       <c r="F69" s="2"/>
@@ -2139,7 +2163,7 @@
       <c r="C70" t="s">
         <v>27</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="7">
         <v>2</v>
       </c>
       <c r="F70" s="2"/>
@@ -2157,7 +2181,7 @@
       <c r="C71" t="s">
         <v>27</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="7">
         <v>3</v>
       </c>
       <c r="F71" s="2"/>
@@ -2175,7 +2199,7 @@
       <c r="C72" t="s">
         <v>15</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="7">
         <v>1</v>
       </c>
       <c r="F72" s="2"/>
@@ -2193,7 +2217,7 @@
       <c r="C73" t="s">
         <v>15</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="7">
         <v>2</v>
       </c>
       <c r="F73" s="2"/>
@@ -2211,7 +2235,7 @@
       <c r="C74" t="s">
         <v>15</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="7">
         <v>3</v>
       </c>
       <c r="F74" s="2"/>
@@ -2229,7 +2253,7 @@
       <c r="C75" t="s">
         <v>27</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="7">
         <v>1</v>
       </c>
       <c r="F75" s="2"/>
@@ -2247,7 +2271,7 @@
       <c r="C76" t="s">
         <v>27</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="7">
         <v>2</v>
       </c>
       <c r="F76" s="2"/>
@@ -2265,7 +2289,7 @@
       <c r="C77" t="s">
         <v>27</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="7">
         <v>3</v>
       </c>
       <c r="F77" s="2"/>
@@ -2283,7 +2307,7 @@
       <c r="C78" t="s">
         <v>15</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="7">
         <v>1</v>
       </c>
       <c r="F78" s="2"/>
@@ -2301,7 +2325,7 @@
       <c r="C79" t="s">
         <v>15</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="7">
         <v>2</v>
       </c>
       <c r="F79" s="2"/>
@@ -2319,7 +2343,7 @@
       <c r="C80" t="s">
         <v>15</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="7">
         <v>3</v>
       </c>
       <c r="F80" s="2"/>
@@ -2327,15 +2351,20 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D81" s="7"/>
+    </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
+      <c r="D82" s="7"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>199</v>
       </c>
+      <c r="D83" s="7"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
@@ -2347,7 +2376,7 @@
       <c r="C84" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -2385,7 +2414,7 @@
       <c r="C85" t="s">
         <v>14</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="7">
         <v>1</v>
       </c>
       <c r="E85" s="2"/>
@@ -2409,7 +2438,7 @@
       <c r="C86" t="s">
         <v>27</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="7">
         <v>1</v>
       </c>
       <c r="F86" s="2"/>
@@ -2427,7 +2456,7 @@
       <c r="C87" t="s">
         <v>27</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="7">
         <v>2</v>
       </c>
       <c r="F87" s="2"/>
@@ -2445,7 +2474,7 @@
       <c r="C88" t="s">
         <v>27</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="7">
         <v>3</v>
       </c>
       <c r="F88" s="2"/>
@@ -2463,7 +2492,7 @@
       <c r="C89" t="s">
         <v>15</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="7">
         <v>1</v>
       </c>
       <c r="F89" s="2"/>
@@ -2481,7 +2510,7 @@
       <c r="C90" t="s">
         <v>15</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="7">
         <v>2</v>
       </c>
       <c r="F90" s="2"/>
@@ -2499,7 +2528,7 @@
       <c r="C91" t="s">
         <v>15</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="7">
         <v>3</v>
       </c>
       <c r="F91" s="2"/>
@@ -2517,7 +2546,7 @@
       <c r="C92" t="s">
         <v>27</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="7">
         <v>1</v>
       </c>
       <c r="F92" s="2"/>
@@ -2535,7 +2564,7 @@
       <c r="C93" t="s">
         <v>27</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="7">
         <v>2</v>
       </c>
       <c r="F93" s="2"/>
@@ -2553,7 +2582,7 @@
       <c r="C94" t="s">
         <v>27</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="7">
         <v>3</v>
       </c>
       <c r="F94" s="2"/>
@@ -2571,7 +2600,7 @@
       <c r="C95" t="s">
         <v>15</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="7">
         <v>1</v>
       </c>
       <c r="F95" s="2"/>
@@ -2589,7 +2618,7 @@
       <c r="C96" t="s">
         <v>15</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="7">
         <v>2</v>
       </c>
       <c r="F96" s="2"/>
@@ -2607,7 +2636,7 @@
       <c r="C97" t="s">
         <v>15</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="7">
         <v>3</v>
       </c>
       <c r="F97" s="2"/>
@@ -2615,10 +2644,14 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D98" s="7"/>
+    </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>200</v>
       </c>
+      <c r="D99" s="7"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
@@ -2630,7 +2663,7 @@
       <c r="C100" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -2668,7 +2701,7 @@
       <c r="C101" t="s">
         <v>14</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="7">
         <v>1</v>
       </c>
       <c r="E101" s="2"/>
@@ -2692,7 +2725,7 @@
       <c r="C102" t="s">
         <v>27</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="7">
         <v>1</v>
       </c>
       <c r="F102" s="2"/>
@@ -2710,7 +2743,7 @@
       <c r="C103" t="s">
         <v>27</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="7">
         <v>2</v>
       </c>
       <c r="F103" s="2"/>
@@ -2728,7 +2761,7 @@
       <c r="C104" t="s">
         <v>27</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="7">
         <v>3</v>
       </c>
       <c r="F104" s="2"/>
@@ -2746,7 +2779,7 @@
       <c r="C105" t="s">
         <v>15</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="7">
         <v>1</v>
       </c>
       <c r="F105" s="2"/>
@@ -2764,7 +2797,7 @@
       <c r="C106" t="s">
         <v>15</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="7">
         <v>2</v>
       </c>
       <c r="F106" s="2"/>
@@ -2782,7 +2815,7 @@
       <c r="C107" t="s">
         <v>15</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="7">
         <v>3</v>
       </c>
       <c r="F107" s="2"/>
@@ -2800,7 +2833,7 @@
       <c r="C108" t="s">
         <v>27</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="7">
         <v>1</v>
       </c>
       <c r="F108" s="2"/>
@@ -2818,7 +2851,7 @@
       <c r="C109" t="s">
         <v>27</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="7">
         <v>2</v>
       </c>
       <c r="F109" s="2"/>
@@ -2836,7 +2869,7 @@
       <c r="C110" t="s">
         <v>27</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="7">
         <v>3</v>
       </c>
       <c r="F110" s="2"/>
@@ -2854,7 +2887,7 @@
       <c r="C111" t="s">
         <v>15</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="7">
         <v>1</v>
       </c>
       <c r="F111" s="2"/>
@@ -2872,7 +2905,7 @@
       <c r="C112" t="s">
         <v>15</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="7">
         <v>2</v>
       </c>
       <c r="F112" s="2"/>
@@ -2890,7 +2923,7 @@
       <c r="C113" t="s">
         <v>15</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="7">
         <v>3</v>
       </c>
       <c r="F113" s="2"/>
@@ -2898,10 +2931,14 @@
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
     </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D114" s="7"/>
+    </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="D115" s="7"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
@@ -2913,7 +2950,7 @@
       <c r="C116" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E116" s="4" t="s">
@@ -2951,7 +2988,7 @@
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D117" s="5">
+      <c r="D117" s="10">
         <v>1</v>
       </c>
       <c r="E117" s="6"/>
@@ -2977,7 +3014,7 @@
       <c r="C118" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="10">
         <v>1</v>
       </c>
       <c r="E118" s="5"/>
@@ -2999,7 +3036,7 @@
       <c r="C119" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="10">
         <v>2</v>
       </c>
       <c r="E119" s="5"/>
@@ -3021,7 +3058,7 @@
       <c r="C120" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="10">
         <v>3</v>
       </c>
       <c r="E120" s="5"/>
@@ -3043,7 +3080,7 @@
       <c r="C121" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="10">
         <v>1</v>
       </c>
       <c r="E121" s="5"/>
@@ -3065,7 +3102,7 @@
       <c r="C122" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="10">
         <v>2</v>
       </c>
       <c r="E122" s="5"/>
@@ -3087,7 +3124,7 @@
       <c r="C123" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="5">
+      <c r="D123" s="10">
         <v>3</v>
       </c>
       <c r="E123" s="5"/>
@@ -3109,7 +3146,7 @@
       <c r="C124" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D124" s="10">
         <v>1</v>
       </c>
       <c r="E124" s="5"/>
@@ -3131,7 +3168,7 @@
       <c r="C125" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D125" s="5">
+      <c r="D125" s="10">
         <v>2</v>
       </c>
       <c r="E125" s="5"/>
@@ -3153,7 +3190,7 @@
       <c r="C126" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="10">
         <v>3</v>
       </c>
       <c r="E126" s="5"/>
@@ -3175,7 +3212,7 @@
       <c r="C127" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="10">
         <v>1</v>
       </c>
       <c r="E127" s="5"/>
@@ -3197,7 +3234,7 @@
       <c r="C128" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="10">
         <v>2</v>
       </c>
       <c r="E128" s="5"/>
@@ -3219,7 +3256,7 @@
       <c r="C129" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="10">
         <v>3</v>
       </c>
       <c r="E129" s="5"/>
@@ -3231,10 +3268,14 @@
       <c r="K129" s="5"/>
       <c r="L129" s="5"/>
     </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D130" s="7"/>
+    </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="D131" s="7"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
@@ -3246,7 +3287,7 @@
       <c r="C132" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E132" s="4" t="s">
@@ -3284,7 +3325,7 @@
       <c r="C133" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="5">
+      <c r="D133" s="10">
         <v>1</v>
       </c>
       <c r="E133" s="6"/>
@@ -3310,7 +3351,7 @@
       <c r="C134" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="10">
         <v>1</v>
       </c>
       <c r="E134" s="5"/>
@@ -3332,7 +3373,7 @@
       <c r="C135" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="10">
         <v>2</v>
       </c>
       <c r="E135" s="5"/>
@@ -3354,7 +3395,7 @@
       <c r="C136" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="10">
         <v>3</v>
       </c>
       <c r="E136" s="5"/>
@@ -3376,7 +3417,7 @@
       <c r="C137" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="10">
         <v>1</v>
       </c>
       <c r="E137" s="5"/>
@@ -3398,7 +3439,7 @@
       <c r="C138" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="10">
         <v>2</v>
       </c>
       <c r="E138" s="5"/>
@@ -3420,7 +3461,7 @@
       <c r="C139" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="10">
         <v>3</v>
       </c>
       <c r="E139" s="5"/>
@@ -3442,7 +3483,7 @@
       <c r="C140" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="10">
         <v>1</v>
       </c>
       <c r="E140" s="5"/>
@@ -3464,7 +3505,7 @@
       <c r="C141" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141" s="10">
         <v>2</v>
       </c>
       <c r="E141" s="5"/>
@@ -3486,7 +3527,7 @@
       <c r="C142" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="10">
         <v>3</v>
       </c>
       <c r="E142" s="5"/>
@@ -3508,7 +3549,7 @@
       <c r="C143" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D143" s="10">
         <v>1</v>
       </c>
       <c r="E143" s="5"/>
@@ -3530,7 +3571,7 @@
       <c r="C144" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="10">
         <v>2</v>
       </c>
       <c r="E144" s="5"/>
@@ -3552,7 +3593,7 @@
       <c r="C145" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D145" s="10">
         <v>3</v>
       </c>
       <c r="E145" s="5"/>
@@ -3564,15 +3605,20 @@
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
     </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D146" s="7"/>
+    </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="D147" s="7"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>195</v>
       </c>
+      <c r="D148" s="7"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
@@ -3584,7 +3630,7 @@
       <c r="C149" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="D149" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E149" s="4" t="s">
@@ -3622,7 +3668,7 @@
       <c r="C150" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150" s="10">
         <v>1</v>
       </c>
       <c r="E150" s="6"/>
@@ -3648,7 +3694,7 @@
       <c r="C151" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151" s="10">
         <v>1</v>
       </c>
       <c r="E151" s="5"/>
@@ -3670,7 +3716,7 @@
       <c r="C152" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D152" s="10">
         <v>2</v>
       </c>
       <c r="E152" s="5"/>
@@ -3692,7 +3738,7 @@
       <c r="C153" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D153" s="10">
         <v>3</v>
       </c>
       <c r="E153" s="5"/>
@@ -3714,7 +3760,7 @@
       <c r="C154" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="10">
         <v>1</v>
       </c>
       <c r="E154" s="5"/>
@@ -3736,7 +3782,7 @@
       <c r="C155" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D155" s="5">
+      <c r="D155" s="10">
         <v>2</v>
       </c>
       <c r="E155" s="5"/>
@@ -3758,7 +3804,7 @@
       <c r="C156" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D156" s="5">
+      <c r="D156" s="10">
         <v>3</v>
       </c>
       <c r="E156" s="5"/>
@@ -3780,7 +3826,7 @@
       <c r="C157" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D157" s="5">
+      <c r="D157" s="10">
         <v>1</v>
       </c>
       <c r="E157" s="5"/>
@@ -3802,7 +3848,7 @@
       <c r="C158" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D158" s="5">
+      <c r="D158" s="10">
         <v>2</v>
       </c>
       <c r="E158" s="5"/>
@@ -3824,7 +3870,7 @@
       <c r="C159" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D159" s="5">
+      <c r="D159" s="10">
         <v>3</v>
       </c>
       <c r="E159" s="5"/>
@@ -3846,7 +3892,7 @@
       <c r="C160" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D160" s="5">
+      <c r="D160" s="10">
         <v>1</v>
       </c>
       <c r="E160" s="5"/>
@@ -3868,7 +3914,7 @@
       <c r="C161" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D161" s="10">
         <v>2</v>
       </c>
       <c r="E161" s="5"/>
@@ -3890,7 +3936,7 @@
       <c r="C162" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D162" s="5">
+      <c r="D162" s="10">
         <v>3</v>
       </c>
       <c r="E162" s="5"/>
@@ -3902,10 +3948,14 @@
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
     </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D163" s="7"/>
+    </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>196</v>
       </c>
+      <c r="D164" s="7"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
@@ -3917,7 +3967,7 @@
       <c r="C165" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E165" s="4" t="s">
@@ -3955,7 +4005,7 @@
       <c r="C166" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D166" s="5">
+      <c r="D166" s="10">
         <v>1</v>
       </c>
       <c r="E166" s="6"/>
@@ -3981,7 +4031,7 @@
       <c r="C167" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D167" s="5">
+      <c r="D167" s="10">
         <v>1</v>
       </c>
       <c r="E167" s="5"/>
@@ -4003,7 +4053,7 @@
       <c r="C168" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D168" s="5">
+      <c r="D168" s="10">
         <v>2</v>
       </c>
       <c r="E168" s="5"/>
@@ -4025,7 +4075,7 @@
       <c r="C169" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D169" s="5">
+      <c r="D169" s="10">
         <v>3</v>
       </c>
       <c r="E169" s="5"/>
@@ -4047,7 +4097,7 @@
       <c r="C170" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D170" s="5">
+      <c r="D170" s="10">
         <v>1</v>
       </c>
       <c r="E170" s="5"/>
@@ -4069,7 +4119,7 @@
       <c r="C171" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D171" s="5">
+      <c r="D171" s="10">
         <v>2</v>
       </c>
       <c r="E171" s="5"/>
@@ -4091,7 +4141,7 @@
       <c r="C172" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D172" s="5">
+      <c r="D172" s="10">
         <v>3</v>
       </c>
       <c r="E172" s="5"/>
@@ -4113,7 +4163,7 @@
       <c r="C173" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D173" s="5">
+      <c r="D173" s="10">
         <v>1</v>
       </c>
       <c r="E173" s="5"/>
@@ -4135,7 +4185,7 @@
       <c r="C174" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D174" s="5">
+      <c r="D174" s="10">
         <v>2</v>
       </c>
       <c r="E174" s="5"/>
@@ -4157,7 +4207,7 @@
       <c r="C175" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D175" s="5">
+      <c r="D175" s="10">
         <v>3</v>
       </c>
       <c r="E175" s="5"/>
@@ -4179,7 +4229,7 @@
       <c r="C176" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D176" s="5">
+      <c r="D176" s="10">
         <v>1</v>
       </c>
       <c r="E176" s="5"/>
@@ -4201,7 +4251,7 @@
       <c r="C177" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D177" s="5">
+      <c r="D177" s="10">
         <v>2</v>
       </c>
       <c r="E177" s="5"/>
@@ -4223,7 +4273,7 @@
       <c r="C178" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D178" s="10">
         <v>3</v>
       </c>
       <c r="E178" s="5"/>
@@ -4235,10 +4285,14 @@
       <c r="K178" s="5"/>
       <c r="L178" s="5"/>
     </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D179" s="7"/>
+    </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="D180" s="7"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
@@ -4250,7 +4304,7 @@
       <c r="C181" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E181" s="4" t="s">
@@ -4288,7 +4342,7 @@
       <c r="C182" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D182" s="10">
         <v>1</v>
       </c>
       <c r="E182" s="6"/>
@@ -4314,7 +4368,7 @@
       <c r="C183" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D183" s="10">
         <v>1</v>
       </c>
       <c r="E183" s="5"/>
@@ -4336,7 +4390,7 @@
       <c r="C184" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D184" s="10">
         <v>2</v>
       </c>
       <c r="E184" s="5"/>
@@ -4358,7 +4412,7 @@
       <c r="C185" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D185" s="5">
+      <c r="D185" s="10">
         <v>3</v>
       </c>
       <c r="E185" s="5"/>
@@ -4380,7 +4434,7 @@
       <c r="C186" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D186" s="10">
         <v>1</v>
       </c>
       <c r="E186" s="5"/>
@@ -4402,7 +4456,7 @@
       <c r="C187" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D187" s="5">
+      <c r="D187" s="10">
         <v>2</v>
       </c>
       <c r="E187" s="5"/>
@@ -4424,7 +4478,7 @@
       <c r="C188" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D188" s="5">
+      <c r="D188" s="10">
         <v>3</v>
       </c>
       <c r="E188" s="5"/>
@@ -4446,7 +4500,7 @@
       <c r="C189" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D189" s="5">
+      <c r="D189" s="10">
         <v>1</v>
       </c>
       <c r="E189" s="5"/>
@@ -4468,7 +4522,7 @@
       <c r="C190" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D190" s="5">
+      <c r="D190" s="10">
         <v>2</v>
       </c>
       <c r="E190" s="5"/>
@@ -4490,7 +4544,7 @@
       <c r="C191" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D191" s="5">
+      <c r="D191" s="10">
         <v>3</v>
       </c>
       <c r="E191" s="5"/>
@@ -4512,7 +4566,7 @@
       <c r="C192" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D192" s="5">
+      <c r="D192" s="10">
         <v>1</v>
       </c>
       <c r="E192" s="5"/>
@@ -4534,7 +4588,7 @@
       <c r="C193" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D193" s="5">
+      <c r="D193" s="10">
         <v>2</v>
       </c>
       <c r="E193" s="5"/>
@@ -4556,7 +4610,7 @@
       <c r="C194" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D194" s="5">
+      <c r="D194" s="10">
         <v>3</v>
       </c>
       <c r="E194" s="5"/>
@@ -4568,10 +4622,14 @@
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
     </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D195" s="7"/>
+    </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="D196" s="7"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
@@ -4583,7 +4641,7 @@
       <c r="C197" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D197" s="4" t="s">
+      <c r="D197" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E197" s="4" t="s">
@@ -4621,7 +4679,7 @@
       <c r="C198" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D198" s="5">
+      <c r="D198" s="10">
         <v>1</v>
       </c>
       <c r="E198" s="6"/>
@@ -4647,7 +4705,7 @@
       <c r="C199" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D199" s="5">
+      <c r="D199" s="10">
         <v>1</v>
       </c>
       <c r="E199" s="5"/>
@@ -4669,7 +4727,7 @@
       <c r="C200" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D200" s="5">
+      <c r="D200" s="10">
         <v>2</v>
       </c>
       <c r="E200" s="5"/>
@@ -4691,7 +4749,7 @@
       <c r="C201" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D201" s="5">
+      <c r="D201" s="10">
         <v>3</v>
       </c>
       <c r="E201" s="5"/>
@@ -4713,7 +4771,7 @@
       <c r="C202" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D202" s="5">
+      <c r="D202" s="10">
         <v>1</v>
       </c>
       <c r="E202" s="5"/>
@@ -4735,7 +4793,7 @@
       <c r="C203" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D203" s="5">
+      <c r="D203" s="10">
         <v>2</v>
       </c>
       <c r="E203" s="5"/>
@@ -4757,7 +4815,7 @@
       <c r="C204" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D204" s="5">
+      <c r="D204" s="10">
         <v>3</v>
       </c>
       <c r="E204" s="5"/>
@@ -4779,7 +4837,7 @@
       <c r="C205" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D205" s="5">
+      <c r="D205" s="10">
         <v>1</v>
       </c>
       <c r="E205" s="5"/>
@@ -4801,7 +4859,7 @@
       <c r="C206" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D206" s="5">
+      <c r="D206" s="10">
         <v>2</v>
       </c>
       <c r="E206" s="5"/>
@@ -4823,7 +4881,7 @@
       <c r="C207" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D207" s="5">
+      <c r="D207" s="10">
         <v>3</v>
       </c>
       <c r="E207" s="5"/>
@@ -4845,7 +4903,7 @@
       <c r="C208" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D208" s="5">
+      <c r="D208" s="10">
         <v>1</v>
       </c>
       <c r="E208" s="5"/>
@@ -4867,7 +4925,7 @@
       <c r="C209" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D209" s="5">
+      <c r="D209" s="10">
         <v>2</v>
       </c>
       <c r="E209" s="5"/>
@@ -4889,7 +4947,7 @@
       <c r="C210" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D210" s="5">
+      <c r="D210" s="10">
         <v>3</v>
       </c>
       <c r="E210" s="5"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4842242F-D130-4AD9-9D36-15D5E930C389}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7A6A6B-2682-40B5-B0C1-3344D646ED02}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17E37448-4081-435B-9D75-A90A063593FC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="203">
   <si>
     <t>Test Case</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>N1: Report on the output of a small controlled network scan.</t>
-  </si>
-  <si>
-    <t>N2: Report on the output of a large network scan with many hosts and a mix of both common and uncommon ports.</t>
   </si>
   <si>
     <t>N3: Report on the output of a network scan containing a filtered or non-responsive host</t>
@@ -715,11 +712,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -750,6 +746,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1089,7 +1089,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1108,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1136,7 +1136,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>1</v>
       </c>
       <c r="B8" t="s">
@@ -1144,7 +1144,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>2</v>
       </c>
       <c r="B9" t="s">
@@ -1152,7 +1152,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
@@ -1160,7 +1160,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
@@ -1168,7 +1168,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
@@ -1176,7 +1176,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>6</v>
       </c>
       <c r="B13" t="s">
@@ -1184,23 +1184,20 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1260,7 +1257,7 @@
       <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>1</v>
       </c>
       <c r="E20" s="2"/>
@@ -1284,7 +1281,7 @@
       <c r="C21" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="6">
         <v>1</v>
       </c>
       <c r="F21" s="2"/>
@@ -1302,7 +1299,7 @@
       <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>2</v>
       </c>
       <c r="F22" s="2"/>
@@ -1320,7 +1317,7 @@
       <c r="C23" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>3</v>
       </c>
       <c r="F23" s="2"/>
@@ -1338,7 +1335,7 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>1</v>
       </c>
       <c r="F24" s="2"/>
@@ -1356,7 +1353,7 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>2</v>
       </c>
       <c r="F25" s="2"/>
@@ -1374,7 +1371,7 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>3</v>
       </c>
       <c r="F26" s="2"/>
@@ -1392,7 +1389,7 @@
       <c r="C27" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>1</v>
       </c>
       <c r="F27" s="2"/>
@@ -1410,7 +1407,7 @@
       <c r="C28" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>2</v>
       </c>
       <c r="F28" s="2"/>
@@ -1428,7 +1425,7 @@
       <c r="C29" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>3</v>
       </c>
       <c r="F29" s="2"/>
@@ -1446,7 +1443,7 @@
       <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>1</v>
       </c>
       <c r="F30" s="2"/>
@@ -1464,7 +1461,7 @@
       <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>2</v>
       </c>
       <c r="F31" s="2"/>
@@ -1482,7 +1479,7 @@
       <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>3</v>
       </c>
       <c r="F32" s="2"/>
@@ -1491,13 +1488,11 @@
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D33" s="7"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="7"/>
+      <c r="A34" s="1"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -1509,7 +1504,7 @@
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -1539,7 +1534,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -1547,7 +1542,7 @@
       <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>1</v>
       </c>
       <c r="E36" s="2"/>
@@ -1563,7 +1558,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -1571,7 +1566,7 @@
       <c r="C37" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>1</v>
       </c>
       <c r="F37" s="2"/>
@@ -1581,7 +1576,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -1589,7 +1584,7 @@
       <c r="C38" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>2</v>
       </c>
       <c r="F38" s="2"/>
@@ -1599,7 +1594,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -1607,7 +1602,7 @@
       <c r="C39" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>3</v>
       </c>
       <c r="F39" s="2"/>
@@ -1617,7 +1612,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -1625,7 +1620,7 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>1</v>
       </c>
       <c r="F40" s="2"/>
@@ -1635,7 +1630,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -1643,7 +1638,7 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>2</v>
       </c>
       <c r="F41" s="2"/>
@@ -1653,7 +1648,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -1661,7 +1656,7 @@
       <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>3</v>
       </c>
       <c r="F42" s="2"/>
@@ -1671,7 +1666,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -1679,7 +1674,7 @@
       <c r="C43" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>1</v>
       </c>
       <c r="F43" s="2"/>
@@ -1689,7 +1684,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -1697,7 +1692,7 @@
       <c r="C44" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>2</v>
       </c>
       <c r="F44" s="2"/>
@@ -1707,7 +1702,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -1715,7 +1710,7 @@
       <c r="C45" t="s">
         <v>27</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>3</v>
       </c>
       <c r="F45" s="2"/>
@@ -1725,7 +1720,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -1733,7 +1728,7 @@
       <c r="C46" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>1</v>
       </c>
       <c r="F46" s="2"/>
@@ -1743,7 +1738,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -1751,7 +1746,7 @@
       <c r="C47" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="6">
         <v>2</v>
       </c>
       <c r="F47" s="2"/>
@@ -1761,7 +1756,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -1769,7 +1764,7 @@
       <c r="C48" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="6">
         <v>3</v>
       </c>
       <c r="F48" s="2"/>
@@ -1778,13 +1773,13 @@
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D49" s="7"/>
+      <c r="D49" s="6"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="D50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -1796,7 +1791,7 @@
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1826,7 +1821,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -1834,7 +1829,7 @@
       <c r="C52" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>1</v>
       </c>
       <c r="E52" s="2"/>
@@ -1850,7 +1845,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -1858,7 +1853,7 @@
       <c r="C53" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>1</v>
       </c>
       <c r="F53" s="2"/>
@@ -1868,7 +1863,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -1876,7 +1871,7 @@
       <c r="C54" t="s">
         <v>27</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>2</v>
       </c>
       <c r="F54" s="2"/>
@@ -1886,7 +1881,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -1894,7 +1889,7 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>3</v>
       </c>
       <c r="F55" s="2"/>
@@ -1904,7 +1899,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -1912,7 +1907,7 @@
       <c r="C56" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>1</v>
       </c>
       <c r="F56" s="2"/>
@@ -1922,7 +1917,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -1930,7 +1925,7 @@
       <c r="C57" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>2</v>
       </c>
       <c r="F57" s="2"/>
@@ -1940,7 +1935,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -1948,7 +1943,7 @@
       <c r="C58" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="6">
         <v>3</v>
       </c>
       <c r="F58" s="2"/>
@@ -1958,7 +1953,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -1966,7 +1961,7 @@
       <c r="C59" t="s">
         <v>27</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="6">
         <v>1</v>
       </c>
       <c r="F59" s="2"/>
@@ -1976,7 +1971,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -1984,7 +1979,7 @@
       <c r="C60" t="s">
         <v>27</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="6">
         <v>2</v>
       </c>
       <c r="F60" s="2"/>
@@ -1994,7 +1989,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -2002,7 +1997,7 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="6">
         <v>3</v>
       </c>
       <c r="F61" s="2"/>
@@ -2012,7 +2007,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -2020,7 +2015,7 @@
       <c r="C62" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="6">
         <v>1</v>
       </c>
       <c r="F62" s="2"/>
@@ -2030,7 +2025,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -2038,7 +2033,7 @@
       <c r="C63" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="6">
         <v>2</v>
       </c>
       <c r="F63" s="2"/>
@@ -2048,7 +2043,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -2056,7 +2051,7 @@
       <c r="C64" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="6">
         <v>3</v>
       </c>
       <c r="F64" s="2"/>
@@ -2065,13 +2060,13 @@
       <c r="I64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D65" s="7"/>
+      <c r="D65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="D66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
@@ -2083,7 +2078,7 @@
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -2113,7 +2108,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
@@ -2121,7 +2116,7 @@
       <c r="C68" t="s">
         <v>14</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>1</v>
       </c>
       <c r="E68" s="2"/>
@@ -2137,7 +2132,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2145,7 +2140,7 @@
       <c r="C69" t="s">
         <v>27</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="6">
         <v>1</v>
       </c>
       <c r="F69" s="2"/>
@@ -2155,7 +2150,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2163,7 +2158,7 @@
       <c r="C70" t="s">
         <v>27</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>2</v>
       </c>
       <c r="F70" s="2"/>
@@ -2173,7 +2168,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -2181,7 +2176,7 @@
       <c r="C71" t="s">
         <v>27</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>3</v>
       </c>
       <c r="F71" s="2"/>
@@ -2191,7 +2186,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -2199,7 +2194,7 @@
       <c r="C72" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="6">
         <v>1</v>
       </c>
       <c r="F72" s="2"/>
@@ -2209,7 +2204,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -2217,7 +2212,7 @@
       <c r="C73" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="6">
         <v>2</v>
       </c>
       <c r="F73" s="2"/>
@@ -2227,7 +2222,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -2235,7 +2230,7 @@
       <c r="C74" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="6">
         <v>3</v>
       </c>
       <c r="F74" s="2"/>
@@ -2245,7 +2240,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -2253,7 +2248,7 @@
       <c r="C75" t="s">
         <v>27</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="6">
         <v>1</v>
       </c>
       <c r="F75" s="2"/>
@@ -2263,7 +2258,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -2271,7 +2266,7 @@
       <c r="C76" t="s">
         <v>27</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="6">
         <v>2</v>
       </c>
       <c r="F76" s="2"/>
@@ -2281,7 +2276,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -2289,7 +2284,7 @@
       <c r="C77" t="s">
         <v>27</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="6">
         <v>3</v>
       </c>
       <c r="F77" s="2"/>
@@ -2299,7 +2294,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -2307,7 +2302,7 @@
       <c r="C78" t="s">
         <v>15</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="6">
         <v>1</v>
       </c>
       <c r="F78" s="2"/>
@@ -2317,7 +2312,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2325,7 +2320,7 @@
       <c r="C79" t="s">
         <v>15</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="6">
         <v>2</v>
       </c>
       <c r="F79" s="2"/>
@@ -2335,7 +2330,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2343,7 +2338,7 @@
       <c r="C80" t="s">
         <v>15</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="6">
         <v>3</v>
       </c>
       <c r="F80" s="2"/>
@@ -2352,19 +2347,19 @@
       <c r="I80" s="2"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D81" s="7"/>
+      <c r="D81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D82" s="7"/>
+        <v>192</v>
+      </c>
+      <c r="D82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="7"/>
+        <v>198</v>
+      </c>
+      <c r="D83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
@@ -2376,7 +2371,7 @@
       <c r="C84" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -2406,7 +2401,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -2414,7 +2409,7 @@
       <c r="C85" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="6">
         <v>1</v>
       </c>
       <c r="E85" s="2"/>
@@ -2430,7 +2425,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -2438,7 +2433,7 @@
       <c r="C86" t="s">
         <v>27</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="6">
         <v>1</v>
       </c>
       <c r="F86" s="2"/>
@@ -2448,7 +2443,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -2456,7 +2451,7 @@
       <c r="C87" t="s">
         <v>27</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="6">
         <v>2</v>
       </c>
       <c r="F87" s="2"/>
@@ -2466,7 +2461,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
@@ -2474,7 +2469,7 @@
       <c r="C88" t="s">
         <v>27</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="6">
         <v>3</v>
       </c>
       <c r="F88" s="2"/>
@@ -2484,7 +2479,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
@@ -2492,7 +2487,7 @@
       <c r="C89" t="s">
         <v>15</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="6">
         <v>1</v>
       </c>
       <c r="F89" s="2"/>
@@ -2502,7 +2497,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -2510,7 +2505,7 @@
       <c r="C90" t="s">
         <v>15</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>2</v>
       </c>
       <c r="F90" s="2"/>
@@ -2520,7 +2515,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
@@ -2528,7 +2523,7 @@
       <c r="C91" t="s">
         <v>15</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="6">
         <v>3</v>
       </c>
       <c r="F91" s="2"/>
@@ -2538,7 +2533,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -2546,7 +2541,7 @@
       <c r="C92" t="s">
         <v>27</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="6">
         <v>1</v>
       </c>
       <c r="F92" s="2"/>
@@ -2556,7 +2551,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -2564,7 +2559,7 @@
       <c r="C93" t="s">
         <v>27</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="6">
         <v>2</v>
       </c>
       <c r="F93" s="2"/>
@@ -2574,7 +2569,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -2582,7 +2577,7 @@
       <c r="C94" t="s">
         <v>27</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="6">
         <v>3</v>
       </c>
       <c r="F94" s="2"/>
@@ -2592,7 +2587,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -2600,7 +2595,7 @@
       <c r="C95" t="s">
         <v>15</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="6">
         <v>1</v>
       </c>
       <c r="F95" s="2"/>
@@ -2610,7 +2605,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -2618,7 +2613,7 @@
       <c r="C96" t="s">
         <v>15</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="6">
         <v>2</v>
       </c>
       <c r="F96" s="2"/>
@@ -2628,7 +2623,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2636,7 +2631,7 @@
       <c r="C97" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="6">
         <v>3</v>
       </c>
       <c r="F97" s="2"/>
@@ -2645,13 +2640,13 @@
       <c r="I97" s="2"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D98" s="7"/>
+      <c r="D98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D99" s="7"/>
+        <v>199</v>
+      </c>
+      <c r="D99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
@@ -2663,7 +2658,7 @@
       <c r="C100" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -2693,7 +2688,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B101" t="s">
         <v>11</v>
@@ -2701,7 +2696,7 @@
       <c r="C101" t="s">
         <v>14</v>
       </c>
-      <c r="D101" s="7">
+      <c r="D101" s="6">
         <v>1</v>
       </c>
       <c r="E101" s="2"/>
@@ -2717,7 +2712,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
@@ -2725,7 +2720,7 @@
       <c r="C102" t="s">
         <v>27</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="6">
         <v>1</v>
       </c>
       <c r="F102" s="2"/>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
@@ -2743,7 +2738,7 @@
       <c r="C103" t="s">
         <v>27</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D103" s="6">
         <v>2</v>
       </c>
       <c r="F103" s="2"/>
@@ -2753,7 +2748,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
@@ -2761,7 +2756,7 @@
       <c r="C104" t="s">
         <v>27</v>
       </c>
-      <c r="D104" s="7">
+      <c r="D104" s="6">
         <v>3</v>
       </c>
       <c r="F104" s="2"/>
@@ -2771,7 +2766,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
@@ -2779,7 +2774,7 @@
       <c r="C105" t="s">
         <v>15</v>
       </c>
-      <c r="D105" s="7">
+      <c r="D105" s="6">
         <v>1</v>
       </c>
       <c r="F105" s="2"/>
@@ -2789,7 +2784,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -2797,7 +2792,7 @@
       <c r="C106" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="7">
+      <c r="D106" s="6">
         <v>2</v>
       </c>
       <c r="F106" s="2"/>
@@ -2807,7 +2802,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
@@ -2815,7 +2810,7 @@
       <c r="C107" t="s">
         <v>15</v>
       </c>
-      <c r="D107" s="7">
+      <c r="D107" s="6">
         <v>3</v>
       </c>
       <c r="F107" s="2"/>
@@ -2825,7 +2820,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -2833,7 +2828,7 @@
       <c r="C108" t="s">
         <v>27</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="6">
         <v>1</v>
       </c>
       <c r="F108" s="2"/>
@@ -2843,7 +2838,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -2851,7 +2846,7 @@
       <c r="C109" t="s">
         <v>27</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D109" s="6">
         <v>2</v>
       </c>
       <c r="F109" s="2"/>
@@ -2861,7 +2856,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -2869,7 +2864,7 @@
       <c r="C110" t="s">
         <v>27</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="6">
         <v>3</v>
       </c>
       <c r="F110" s="2"/>
@@ -2879,7 +2874,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -2887,7 +2882,7 @@
       <c r="C111" t="s">
         <v>15</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="6">
         <v>1</v>
       </c>
       <c r="F111" s="2"/>
@@ -2897,7 +2892,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -2905,7 +2900,7 @@
       <c r="C112" t="s">
         <v>15</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="6">
         <v>2</v>
       </c>
       <c r="F112" s="2"/>
@@ -2915,7 +2910,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -2923,7 +2918,7 @@
       <c r="C113" t="s">
         <v>15</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D113" s="6">
         <v>3</v>
       </c>
       <c r="F113" s="2"/>
@@ -2932,2032 +2927,2032 @@
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D114" s="7"/>
+      <c r="D114" s="6"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D115" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="D115" s="6"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D116" s="9" t="s">
+      <c r="D116" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H116" s="4" t="s">
+      <c r="E116" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H116" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I116" s="4" t="s">
+      <c r="I116" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J116" s="4" t="s">
+      <c r="J116" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K116" s="4" t="s">
+      <c r="K116" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L116" s="4" t="s">
+      <c r="L116" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>112</v>
-      </c>
-      <c r="B117" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B117" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="C117" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D117" s="10">
-        <v>1</v>
-      </c>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5" t="s">
+      <c r="D117" s="9">
+        <v>1</v>
+      </c>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K117" s="5" t="s">
+      <c r="K117" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L117" s="5"/>
+      <c r="L117" s="4"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>113</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D118" s="10">
-        <v>1</v>
-      </c>
-      <c r="E118" s="5"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D118" s="9">
+        <v>1</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>114</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D119" s="10">
-        <v>2</v>
-      </c>
-      <c r="E119" s="5"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="5"/>
+        <v>113</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D119" s="9">
+        <v>2</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>115</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D120" s="10">
-        <v>3</v>
-      </c>
-      <c r="E120" s="5"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="5"/>
-      <c r="K120" s="5"/>
-      <c r="L120" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120" s="9">
+        <v>3</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="4"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>116</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D121" s="10">
-        <v>1</v>
-      </c>
-      <c r="E121" s="5"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="5"/>
-      <c r="K121" s="5"/>
-      <c r="L121" s="5"/>
+        <v>115</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" s="9">
+        <v>1</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>117</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D122" s="10">
-        <v>2</v>
-      </c>
-      <c r="E122" s="5"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="5"/>
-      <c r="K122" s="5"/>
-      <c r="L122" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="9">
+        <v>2</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="4"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>118</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D123" s="10">
-        <v>3</v>
-      </c>
-      <c r="E123" s="5"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="5"/>
-      <c r="K123" s="5"/>
-      <c r="L123" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="9">
+        <v>3</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>119</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D124" s="10">
-        <v>1</v>
-      </c>
-      <c r="E124" s="5"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="5"/>
-      <c r="K124" s="5"/>
-      <c r="L124" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D124" s="9">
+        <v>1</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+      <c r="L124" s="4"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>120</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D125" s="10">
-        <v>2</v>
-      </c>
-      <c r="E125" s="5"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="5"/>
-      <c r="K125" s="5"/>
-      <c r="L125" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D125" s="9">
+        <v>2</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+      <c r="L125" s="4"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>121</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D126" s="10">
-        <v>3</v>
-      </c>
-      <c r="E126" s="5"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="5"/>
-      <c r="K126" s="5"/>
-      <c r="L126" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" s="9">
+        <v>3</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="4"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>122</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D127" s="10">
-        <v>1</v>
-      </c>
-      <c r="E127" s="5"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5"/>
-      <c r="L127" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="9">
+        <v>1</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>123</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D128" s="10">
-        <v>2</v>
-      </c>
-      <c r="E128" s="5"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="5"/>
-      <c r="K128" s="5"/>
-      <c r="L128" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="9">
+        <v>2</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+      <c r="L128" s="4"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>124</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D129" s="10">
-        <v>3</v>
-      </c>
-      <c r="E129" s="5"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="9">
+        <v>3</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D130" s="7"/>
+      <c r="D130" s="6"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D131" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="D131" s="6"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D132" s="9" t="s">
+      <c r="D132" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E132" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H132" s="4" t="s">
+      <c r="E132" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H132" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I132" s="4" t="s">
+      <c r="I132" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J132" s="4" t="s">
+      <c r="J132" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K132" s="4" t="s">
+      <c r="K132" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L132" s="4" t="s">
+      <c r="L132" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>125</v>
-      </c>
-      <c r="B133" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="C133" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="10">
-        <v>1</v>
-      </c>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="5" t="s">
+      <c r="D133" s="9">
+        <v>1</v>
+      </c>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K133" s="5" t="s">
+      <c r="K133" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L133" s="5"/>
+      <c r="L133" s="4"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>126</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D134" s="10">
-        <v>1</v>
-      </c>
-      <c r="E134" s="5"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="5"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D134" s="9">
+        <v>1</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="4"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>127</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135" s="10">
-        <v>2</v>
-      </c>
-      <c r="E135" s="5"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135" s="9">
+        <v>2</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
+      <c r="L135" s="4"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>128</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D136" s="10">
-        <v>3</v>
-      </c>
-      <c r="E136" s="5"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136" s="9">
+        <v>3</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="4"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D137" s="10">
-        <v>1</v>
-      </c>
-      <c r="E137" s="5"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="5"/>
+        <v>128</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="9">
+        <v>1</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+      <c r="L137" s="4"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>130</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D138" s="10">
-        <v>2</v>
-      </c>
-      <c r="E138" s="5"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="5"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="5"/>
+        <v>129</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="9">
+        <v>2</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+      <c r="L138" s="4"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>131</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D139" s="10">
-        <v>3</v>
-      </c>
-      <c r="E139" s="5"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="5"/>
+        <v>130</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="9">
+        <v>3</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+      <c r="L139" s="4"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>132</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D140" s="10">
-        <v>1</v>
-      </c>
-      <c r="E140" s="5"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D140" s="9">
+        <v>1</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
+      <c r="L140" s="4"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>133</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D141" s="10">
-        <v>2</v>
-      </c>
-      <c r="E141" s="5"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="9">
+        <v>2</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+      <c r="L141" s="4"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>134</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D142" s="10">
-        <v>3</v>
-      </c>
-      <c r="E142" s="5"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="5"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D142" s="9">
+        <v>3</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+      <c r="L142" s="4"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>135</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D143" s="10">
-        <v>1</v>
-      </c>
-      <c r="E143" s="5"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="5"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D143" s="9">
+        <v>1</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+      <c r="L143" s="4"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>136</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D144" s="10">
-        <v>2</v>
-      </c>
-      <c r="E144" s="5"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" s="9">
+        <v>2</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+      <c r="L144" s="4"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>137</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D145" s="10">
-        <v>3</v>
-      </c>
-      <c r="E145" s="5"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" s="9">
+        <v>3</v>
+      </c>
+      <c r="E145" s="4"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+      <c r="L145" s="4"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D146" s="7"/>
+      <c r="D146" s="6"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D147" s="7"/>
+        <v>193</v>
+      </c>
+      <c r="D147" s="6"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D148" s="7"/>
+        <v>194</v>
+      </c>
+      <c r="D148" s="6"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D149" s="9" t="s">
+      <c r="D149" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E149" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H149" s="4" t="s">
+      <c r="E149" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H149" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I149" s="4" t="s">
+      <c r="I149" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J149" s="4" t="s">
+      <c r="J149" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K149" s="4" t="s">
+      <c r="K149" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L149" s="4" t="s">
+      <c r="L149" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>138</v>
-      </c>
-      <c r="B150" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D150" s="10">
-        <v>1</v>
-      </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="5"/>
-      <c r="J150" s="5" t="s">
+      <c r="D150" s="9">
+        <v>1</v>
+      </c>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K150" s="5" t="s">
+      <c r="K150" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L150" s="5"/>
+      <c r="L150" s="4"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>139</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D151" s="10">
-        <v>1</v>
-      </c>
-      <c r="E151" s="5"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="5"/>
-      <c r="K151" s="5"/>
-      <c r="L151" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D151" s="9">
+        <v>1</v>
+      </c>
+      <c r="E151" s="4"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+      <c r="L151" s="4"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>140</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D152" s="10">
-        <v>2</v>
-      </c>
-      <c r="E152" s="5"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="5"/>
-      <c r="L152" s="5"/>
+        <v>139</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D152" s="9">
+        <v>2</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+      <c r="L152" s="4"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>141</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D153" s="10">
-        <v>3</v>
-      </c>
-      <c r="E153" s="5"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="5"/>
-      <c r="K153" s="5"/>
-      <c r="L153" s="5"/>
+        <v>140</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="9">
+        <v>3</v>
+      </c>
+      <c r="E153" s="4"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>142</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D154" s="10">
-        <v>1</v>
-      </c>
-      <c r="E154" s="5"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="5"/>
-      <c r="K154" s="5"/>
-      <c r="L154" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" s="9">
+        <v>1</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="4"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>143</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D155" s="10">
-        <v>2</v>
-      </c>
-      <c r="E155" s="5"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="5"/>
-      <c r="K155" s="5"/>
-      <c r="L155" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="9">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+      <c r="L155" s="4"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>144</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D156" s="10">
-        <v>3</v>
-      </c>
-      <c r="E156" s="5"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="5"/>
-      <c r="K156" s="5"/>
-      <c r="L156" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" s="9">
+        <v>3</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="4"/>
+      <c r="K156" s="4"/>
+      <c r="L156" s="4"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>145</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D157" s="10">
-        <v>1</v>
-      </c>
-      <c r="E157" s="5"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="5"/>
-      <c r="K157" s="5"/>
-      <c r="L157" s="5"/>
+        <v>144</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D157" s="9">
+        <v>1</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="4"/>
+      <c r="K157" s="4"/>
+      <c r="L157" s="4"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>146</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D158" s="10">
-        <v>2</v>
-      </c>
-      <c r="E158" s="5"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="5"/>
-      <c r="K158" s="5"/>
-      <c r="L158" s="5"/>
+        <v>145</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" s="9">
+        <v>2</v>
+      </c>
+      <c r="E158" s="4"/>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="4"/>
+      <c r="L158" s="4"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>147</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D159" s="10">
-        <v>3</v>
-      </c>
-      <c r="E159" s="5"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="5"/>
-      <c r="K159" s="5"/>
-      <c r="L159" s="5"/>
+        <v>146</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D159" s="9">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="4"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>148</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D160" s="10">
-        <v>1</v>
-      </c>
-      <c r="E160" s="5"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
-      <c r="L160" s="5"/>
+        <v>147</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160" s="9">
+        <v>1</v>
+      </c>
+      <c r="E160" s="4"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
+      <c r="L160" s="4"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>149</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D161" s="10">
-        <v>2</v>
-      </c>
-      <c r="E161" s="5"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="5"/>
-      <c r="K161" s="5"/>
-      <c r="L161" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" s="9">
+        <v>2</v>
+      </c>
+      <c r="E161" s="4"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+      <c r="L161" s="4"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>150</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D162" s="10">
-        <v>3</v>
-      </c>
-      <c r="E162" s="5"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="5"/>
-      <c r="K162" s="5"/>
-      <c r="L162" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D162" s="9">
+        <v>3</v>
+      </c>
+      <c r="E162" s="4"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+      <c r="J162" s="4"/>
+      <c r="K162" s="4"/>
+      <c r="L162" s="4"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D163" s="7"/>
+      <c r="D163" s="6"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D164" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="D164" s="6"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D165" s="9" t="s">
+      <c r="D165" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E165" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F165" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G165" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H165" s="4" t="s">
+      <c r="E165" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I165" s="4" t="s">
+      <c r="I165" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J165" s="4" t="s">
+      <c r="J165" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K165" s="4" t="s">
+      <c r="K165" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L165" s="4" t="s">
+      <c r="L165" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>151</v>
-      </c>
-      <c r="B166" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C166" s="5" t="s">
+      <c r="C166" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D166" s="10">
-        <v>1</v>
-      </c>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="5"/>
-      <c r="J166" s="5" t="s">
+      <c r="D166" s="9">
+        <v>1</v>
+      </c>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="4"/>
+      <c r="J166" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K166" s="5" t="s">
+      <c r="K166" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L166" s="5"/>
+      <c r="L166" s="4"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>152</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D167" s="10">
-        <v>1</v>
-      </c>
-      <c r="E167" s="5"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="5"/>
-      <c r="K167" s="5"/>
-      <c r="L167" s="5"/>
+        <v>151</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167" s="9">
+        <v>1</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
+      <c r="L167" s="4"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>153</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D168" s="10">
-        <v>2</v>
-      </c>
-      <c r="E168" s="5"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="5"/>
-      <c r="K168" s="5"/>
-      <c r="L168" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" s="9">
+        <v>2</v>
+      </c>
+      <c r="E168" s="4"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
+      <c r="L168" s="4"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>154</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D169" s="10">
-        <v>3</v>
-      </c>
-      <c r="E169" s="5"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="5"/>
-      <c r="K169" s="5"/>
-      <c r="L169" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" s="9">
+        <v>3</v>
+      </c>
+      <c r="E169" s="4"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+      <c r="L169" s="4"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>155</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D170" s="10">
-        <v>1</v>
-      </c>
-      <c r="E170" s="5"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="5"/>
-      <c r="K170" s="5"/>
-      <c r="L170" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="9">
+        <v>1</v>
+      </c>
+      <c r="E170" s="4"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
+      <c r="L170" s="4"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>156</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D171" s="10">
-        <v>2</v>
-      </c>
-      <c r="E171" s="5"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="5"/>
-      <c r="K171" s="5"/>
-      <c r="L171" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" s="9">
+        <v>2</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+      <c r="L171" s="4"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>157</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D172" s="10">
-        <v>3</v>
-      </c>
-      <c r="E172" s="5"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="5"/>
-      <c r="K172" s="5"/>
-      <c r="L172" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D172" s="9">
+        <v>3</v>
+      </c>
+      <c r="E172" s="4"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+      <c r="L172" s="4"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>158</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D173" s="10">
-        <v>1</v>
-      </c>
-      <c r="E173" s="5"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="5"/>
-      <c r="K173" s="5"/>
-      <c r="L173" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173" s="9">
+        <v>1</v>
+      </c>
+      <c r="E173" s="4"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
+      <c r="L173" s="4"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>159</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D174" s="10">
-        <v>2</v>
-      </c>
-      <c r="E174" s="5"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="5"/>
-      <c r="K174" s="5"/>
-      <c r="L174" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D174" s="9">
+        <v>2</v>
+      </c>
+      <c r="E174" s="4"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="4"/>
+      <c r="K174" s="4"/>
+      <c r="L174" s="4"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>160</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D175" s="10">
-        <v>3</v>
-      </c>
-      <c r="E175" s="5"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="5"/>
-      <c r="K175" s="5"/>
-      <c r="L175" s="5"/>
+        <v>159</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175" s="9">
+        <v>3</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="4"/>
+      <c r="K175" s="4"/>
+      <c r="L175" s="4"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>161</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D176" s="10">
-        <v>1</v>
-      </c>
-      <c r="E176" s="5"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="5"/>
-      <c r="K176" s="5"/>
-      <c r="L176" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D176" s="9">
+        <v>1</v>
+      </c>
+      <c r="E176" s="4"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="4"/>
+      <c r="K176" s="4"/>
+      <c r="L176" s="4"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>162</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D177" s="10">
-        <v>2</v>
-      </c>
-      <c r="E177" s="5"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="5"/>
-      <c r="K177" s="5"/>
-      <c r="L177" s="5"/>
+        <v>161</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D177" s="9">
+        <v>2</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="H177" s="5"/>
+      <c r="I177" s="5"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+      <c r="L177" s="4"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>163</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D178" s="10">
-        <v>3</v>
-      </c>
-      <c r="E178" s="5"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="5"/>
-      <c r="K178" s="5"/>
-      <c r="L178" s="5"/>
+        <v>162</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" s="9">
+        <v>3</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="5"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="4"/>
+      <c r="L178" s="4"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D179" s="7"/>
+      <c r="D179" s="6"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D180" s="7"/>
+        <v>196</v>
+      </c>
+      <c r="D180" s="6"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D181" s="9" t="s">
+      <c r="D181" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E181" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F181" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H181" s="4" t="s">
+      <c r="E181" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H181" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I181" s="4" t="s">
+      <c r="I181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J181" s="4" t="s">
+      <c r="J181" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K181" s="4" t="s">
+      <c r="K181" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L181" s="4" t="s">
+      <c r="L181" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>164</v>
-      </c>
-      <c r="B182" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B182" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C182" s="5" t="s">
+      <c r="C182" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D182" s="10">
-        <v>1</v>
-      </c>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="5"/>
-      <c r="J182" s="5" t="s">
+      <c r="D182" s="9">
+        <v>1</v>
+      </c>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5"/>
+      <c r="G182" s="5"/>
+      <c r="H182" s="5"/>
+      <c r="I182" s="4"/>
+      <c r="J182" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K182" s="5" t="s">
+      <c r="K182" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L182" s="5"/>
+      <c r="L182" s="4"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>165</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D183" s="10">
-        <v>1</v>
-      </c>
-      <c r="E183" s="5"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="5"/>
-      <c r="K183" s="5"/>
-      <c r="L183" s="5"/>
+        <v>164</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D183" s="9">
+        <v>1</v>
+      </c>
+      <c r="E183" s="4"/>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
+      <c r="I183" s="5"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
+      <c r="L183" s="4"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>166</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D184" s="10">
-        <v>2</v>
-      </c>
-      <c r="E184" s="5"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="5"/>
-      <c r="K184" s="5"/>
-      <c r="L184" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D184" s="9">
+        <v>2</v>
+      </c>
+      <c r="E184" s="4"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5"/>
+      <c r="J184" s="4"/>
+      <c r="K184" s="4"/>
+      <c r="L184" s="4"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>167</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D185" s="10">
-        <v>3</v>
-      </c>
-      <c r="E185" s="5"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="5"/>
-      <c r="K185" s="5"/>
-      <c r="L185" s="5"/>
+        <v>166</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D185" s="9">
+        <v>3</v>
+      </c>
+      <c r="E185" s="4"/>
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
+      <c r="L185" s="4"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>168</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D186" s="10">
-        <v>1</v>
-      </c>
-      <c r="E186" s="5"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="5"/>
-      <c r="K186" s="5"/>
-      <c r="L186" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" s="9">
+        <v>1</v>
+      </c>
+      <c r="E186" s="4"/>
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="5"/>
+      <c r="J186" s="4"/>
+      <c r="K186" s="4"/>
+      <c r="L186" s="4"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>169</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D187" s="10">
-        <v>2</v>
-      </c>
-      <c r="E187" s="5"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="5"/>
-      <c r="K187" s="5"/>
-      <c r="L187" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187" s="9">
+        <v>2</v>
+      </c>
+      <c r="E187" s="4"/>
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+      <c r="I187" s="5"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
+      <c r="L187" s="4"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>170</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D188" s="10">
-        <v>3</v>
-      </c>
-      <c r="E188" s="5"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="5"/>
-      <c r="K188" s="5"/>
-      <c r="L188" s="5"/>
+        <v>169</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D188" s="9">
+        <v>3</v>
+      </c>
+      <c r="E188" s="4"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="4"/>
+      <c r="L188" s="4"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>171</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D189" s="10">
-        <v>1</v>
-      </c>
-      <c r="E189" s="5"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="5"/>
-      <c r="K189" s="5"/>
-      <c r="L189" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D189" s="9">
+        <v>1</v>
+      </c>
+      <c r="E189" s="4"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+      <c r="L189" s="4"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>172</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D190" s="10">
-        <v>2</v>
-      </c>
-      <c r="E190" s="5"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="5"/>
-      <c r="K190" s="5"/>
-      <c r="L190" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D190" s="9">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4"/>
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+      <c r="I190" s="5"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="4"/>
+      <c r="L190" s="4"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>173</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D191" s="10">
-        <v>3</v>
-      </c>
-      <c r="E191" s="5"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="5"/>
-      <c r="K191" s="5"/>
-      <c r="L191" s="5"/>
+        <v>172</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D191" s="9">
+        <v>3</v>
+      </c>
+      <c r="E191" s="4"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
+      <c r="I191" s="5"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
+      <c r="L191" s="4"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>174</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D192" s="10">
-        <v>1</v>
-      </c>
-      <c r="E192" s="5"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="5"/>
-      <c r="K192" s="5"/>
-      <c r="L192" s="5"/>
+        <v>173</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D192" s="9">
+        <v>1</v>
+      </c>
+      <c r="E192" s="4"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="5"/>
+      <c r="J192" s="4"/>
+      <c r="K192" s="4"/>
+      <c r="L192" s="4"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>175</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D193" s="10">
-        <v>2</v>
-      </c>
-      <c r="E193" s="5"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="5"/>
-      <c r="K193" s="5"/>
-      <c r="L193" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D193" s="9">
+        <v>2</v>
+      </c>
+      <c r="E193" s="4"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
+      <c r="L193" s="4"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>176</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D194" s="10">
-        <v>3</v>
-      </c>
-      <c r="E194" s="5"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="5"/>
-      <c r="K194" s="5"/>
-      <c r="L194" s="5"/>
+        <v>175</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D194" s="9">
+        <v>3</v>
+      </c>
+      <c r="E194" s="4"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="4"/>
+      <c r="K194" s="4"/>
+      <c r="L194" s="4"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D195" s="7"/>
+      <c r="D195" s="6"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D196" s="7"/>
+        <v>197</v>
+      </c>
+      <c r="D196" s="6"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D197" s="9" t="s">
+      <c r="D197" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E197" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F197" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G197" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H197" s="4" t="s">
+      <c r="E197" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H197" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I197" s="4" t="s">
+      <c r="I197" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J197" s="4" t="s">
+      <c r="J197" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K197" s="4" t="s">
+      <c r="K197" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L197" s="4" t="s">
+      <c r="L197" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>177</v>
-      </c>
-      <c r="B198" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C198" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D198" s="10">
-        <v>1</v>
-      </c>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="5"/>
-      <c r="J198" s="5" t="s">
+      <c r="D198" s="9">
+        <v>1</v>
+      </c>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+      <c r="I198" s="4"/>
+      <c r="J198" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K198" s="5" t="s">
+      <c r="K198" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L198" s="5"/>
+      <c r="L198" s="4"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>178</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D199" s="10">
-        <v>1</v>
-      </c>
-      <c r="E199" s="5"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="5"/>
-      <c r="K199" s="5"/>
-      <c r="L199" s="5"/>
+        <v>177</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D199" s="9">
+        <v>1</v>
+      </c>
+      <c r="E199" s="4"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5"/>
+      <c r="J199" s="4"/>
+      <c r="K199" s="4"/>
+      <c r="L199" s="4"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>179</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D200" s="10">
-        <v>2</v>
-      </c>
-      <c r="E200" s="5"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="5"/>
-      <c r="K200" s="5"/>
-      <c r="L200" s="5"/>
+        <v>178</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D200" s="9">
+        <v>2</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5"/>
+      <c r="J200" s="4"/>
+      <c r="K200" s="4"/>
+      <c r="L200" s="4"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>180</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D201" s="10">
-        <v>3</v>
-      </c>
-      <c r="E201" s="5"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="5"/>
-      <c r="K201" s="5"/>
-      <c r="L201" s="5"/>
+        <v>179</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" s="9">
+        <v>3</v>
+      </c>
+      <c r="E201" s="4"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+      <c r="I201" s="5"/>
+      <c r="J201" s="4"/>
+      <c r="K201" s="4"/>
+      <c r="L201" s="4"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>181</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D202" s="10">
-        <v>1</v>
-      </c>
-      <c r="E202" s="5"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-      <c r="J202" s="5"/>
-      <c r="K202" s="5"/>
-      <c r="L202" s="5"/>
+        <v>180</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202" s="9">
+        <v>1</v>
+      </c>
+      <c r="E202" s="4"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+      <c r="H202" s="5"/>
+      <c r="I202" s="5"/>
+      <c r="J202" s="4"/>
+      <c r="K202" s="4"/>
+      <c r="L202" s="4"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>182</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D203" s="10">
-        <v>2</v>
-      </c>
-      <c r="E203" s="5"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="5"/>
-      <c r="K203" s="5"/>
-      <c r="L203" s="5"/>
+        <v>181</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203" s="9">
+        <v>2</v>
+      </c>
+      <c r="E203" s="4"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="H203" s="5"/>
+      <c r="I203" s="5"/>
+      <c r="J203" s="4"/>
+      <c r="K203" s="4"/>
+      <c r="L203" s="4"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>183</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D204" s="10">
-        <v>3</v>
-      </c>
-      <c r="E204" s="5"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="5"/>
-      <c r="K204" s="5"/>
-      <c r="L204" s="5"/>
+        <v>182</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204" s="9">
+        <v>3</v>
+      </c>
+      <c r="E204" s="4"/>
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5"/>
+      <c r="J204" s="4"/>
+      <c r="K204" s="4"/>
+      <c r="L204" s="4"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>184</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D205" s="10">
-        <v>1</v>
-      </c>
-      <c r="E205" s="5"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
-      <c r="J205" s="5"/>
-      <c r="K205" s="5"/>
-      <c r="L205" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D205" s="9">
+        <v>1</v>
+      </c>
+      <c r="E205" s="4"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="5"/>
+      <c r="J205" s="4"/>
+      <c r="K205" s="4"/>
+      <c r="L205" s="4"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>185</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D206" s="10">
-        <v>2</v>
-      </c>
-      <c r="E206" s="5"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
-      <c r="J206" s="5"/>
-      <c r="K206" s="5"/>
-      <c r="L206" s="5"/>
+        <v>184</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206" s="9">
+        <v>2</v>
+      </c>
+      <c r="E206" s="4"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+      <c r="I206" s="5"/>
+      <c r="J206" s="4"/>
+      <c r="K206" s="4"/>
+      <c r="L206" s="4"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>186</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D207" s="10">
-        <v>3</v>
-      </c>
-      <c r="E207" s="5"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="5"/>
-      <c r="K207" s="5"/>
-      <c r="L207" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D207" s="9">
+        <v>3</v>
+      </c>
+      <c r="E207" s="4"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
+      <c r="J207" s="4"/>
+      <c r="K207" s="4"/>
+      <c r="L207" s="4"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>187</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D208" s="10">
-        <v>1</v>
-      </c>
-      <c r="E208" s="5"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
-      <c r="J208" s="5"/>
-      <c r="K208" s="5"/>
-      <c r="L208" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208" s="9">
+        <v>1</v>
+      </c>
+      <c r="E208" s="4"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="5"/>
+      <c r="H208" s="5"/>
+      <c r="I208" s="5"/>
+      <c r="J208" s="4"/>
+      <c r="K208" s="4"/>
+      <c r="L208" s="4"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>188</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D209" s="10">
-        <v>2</v>
-      </c>
-      <c r="E209" s="5"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
-      <c r="J209" s="5"/>
-      <c r="K209" s="5"/>
-      <c r="L209" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209" s="9">
+        <v>2</v>
+      </c>
+      <c r="E209" s="4"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="5"/>
+      <c r="I209" s="5"/>
+      <c r="J209" s="4"/>
+      <c r="K209" s="4"/>
+      <c r="L209" s="4"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>189</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D210" s="10">
-        <v>3</v>
-      </c>
-      <c r="E210" s="5"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
-      <c r="I210" s="6"/>
-      <c r="J210" s="5"/>
-      <c r="K210" s="5"/>
-      <c r="L210" s="5"/>
+        <v>188</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210" s="9">
+        <v>3</v>
+      </c>
+      <c r="E210" s="4"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+      <c r="H210" s="5"/>
+      <c r="I210" s="5"/>
+      <c r="J210" s="4"/>
+      <c r="K210" s="4"/>
+      <c r="L210" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7A6A6B-2682-40B5-B0C1-3344D646ED02}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{145ACD8D-9A2A-4EC1-BE34-8FCA49626E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A97E743-D5B6-46E2-A0C5-886E857FE9CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17E37448-4081-435B-9D75-A90A063593FC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="198">
   <si>
     <t>Test Case</t>
   </si>
@@ -131,15 +131,6 @@
     <t>N1-AS3</t>
   </si>
   <si>
-    <t>N1-AE1</t>
-  </si>
-  <si>
-    <t>N1-AE2</t>
-  </si>
-  <si>
-    <t>N1-AE3</t>
-  </si>
-  <si>
     <t>N1-BS1</t>
   </si>
   <si>
@@ -149,15 +140,6 @@
     <t>N1-BS3</t>
   </si>
   <si>
-    <t>N1-BE1</t>
-  </si>
-  <si>
-    <t>N1-BE2</t>
-  </si>
-  <si>
-    <t>N1-BE3</t>
-  </si>
-  <si>
     <t>Run</t>
   </si>
   <si>
@@ -648,6 +630,9 @@
   </si>
   <si>
     <t>Did the AI refuse to process poor quality data, or just degrade in quality? (refused, degraded, or n/a).</t>
+  </si>
+  <si>
+    <t>N2: Report on the output of a… Bigger scan idk</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1074,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
@@ -1100,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1108,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,15 +1101,15 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1188,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1201,12 +1186,12 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1220,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>1</v>
@@ -1330,10 +1315,10 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
@@ -1348,10 +1333,10 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D25" s="6">
         <v>2</v>
@@ -1366,10 +1351,10 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D26" s="6">
         <v>3</v>
@@ -1380,108 +1365,42 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
+      <c r="D27" s="6"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
+      <c r="D28" s="6"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="6">
-        <v>3</v>
-      </c>
+      <c r="D29" s="6"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
+      <c r="D30" s="6"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="6">
-        <v>2</v>
-      </c>
+      <c r="D31" s="6"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="6">
-        <v>3</v>
-      </c>
+      <c r="D32" s="6"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -1491,7 +1410,9 @@
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -1505,7 +1426,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>1</v>
@@ -1534,7 +1455,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -1558,7 +1479,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -1576,7 +1497,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -1594,7 +1515,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -1612,7 +1533,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -1630,7 +1551,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -1648,7 +1569,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -1666,7 +1587,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -1684,7 +1605,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -1702,7 +1623,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -1720,7 +1641,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -1738,7 +1659,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -1756,7 +1677,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -1777,7 +1698,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D50" s="6"/>
     </row>
@@ -1792,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>1</v>
@@ -1821,7 +1742,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -1845,7 +1766,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -1863,7 +1784,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -1881,7 +1802,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -1899,7 +1820,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -1917,7 +1838,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -1935,7 +1856,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -1953,7 +1874,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -1971,7 +1892,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -1989,7 +1910,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -2007,7 +1928,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -2025,7 +1946,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -2043,7 +1964,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -2064,7 +1985,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D66" s="6"/>
     </row>
@@ -2079,7 +2000,7 @@
         <v>10</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>1</v>
@@ -2108,7 +2029,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
@@ -2132,7 +2053,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2150,7 +2071,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2168,7 +2089,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -2186,7 +2107,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -2204,7 +2125,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -2222,7 +2143,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -2240,7 +2161,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -2258,7 +2179,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -2276,7 +2197,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -2294,7 +2215,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -2312,7 +2233,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -2330,7 +2251,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -2351,13 +2272,13 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D83" s="6"/>
     </row>
@@ -2372,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>1</v>
@@ -2401,7 +2322,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -2425,7 +2346,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -2443,7 +2364,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -2461,7 +2382,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
@@ -2479,7 +2400,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
@@ -2497,7 +2418,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -2515,7 +2436,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
@@ -2533,7 +2454,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -2551,7 +2472,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -2569,7 +2490,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -2587,7 +2508,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -2605,7 +2526,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -2623,7 +2544,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -2644,7 +2565,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D99" s="6"/>
     </row>
@@ -2659,7 +2580,7 @@
         <v>10</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>1</v>
@@ -2688,7 +2609,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B101" t="s">
         <v>11</v>
@@ -2712,7 +2633,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
@@ -2730,7 +2651,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
@@ -2748,7 +2669,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
@@ -2766,7 +2687,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
@@ -2784,7 +2705,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -2802,7 +2723,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
@@ -2820,7 +2741,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -2838,7 +2759,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -2856,7 +2777,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -2874,7 +2795,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -2892,7 +2813,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -2910,7 +2831,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -2931,7 +2852,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D115" s="6"/>
     </row>
@@ -2946,7 +2867,7 @@
         <v>10</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>1</v>
@@ -2975,7 +2896,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>11</v>
@@ -3001,7 +2922,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>12</v>
@@ -3023,7 +2944,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>12</v>
@@ -3045,7 +2966,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>12</v>
@@ -3067,7 +2988,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>12</v>
@@ -3089,7 +3010,7 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>12</v>
@@ -3111,7 +3032,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>12</v>
@@ -3133,7 +3054,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>13</v>
@@ -3155,7 +3076,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>13</v>
@@ -3177,7 +3098,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>13</v>
@@ -3199,7 +3120,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>13</v>
@@ -3221,7 +3142,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>13</v>
@@ -3243,7 +3164,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>13</v>
@@ -3268,7 +3189,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D131" s="6"/>
     </row>
@@ -3283,7 +3204,7 @@
         <v>10</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>1</v>
@@ -3312,7 +3233,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>11</v>
@@ -3338,7 +3259,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>12</v>
@@ -3360,7 +3281,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>12</v>
@@ -3382,7 +3303,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>12</v>
@@ -3404,7 +3325,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>12</v>
@@ -3426,7 +3347,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>12</v>
@@ -3448,7 +3369,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>12</v>
@@ -3470,7 +3391,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>13</v>
@@ -3492,7 +3413,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>13</v>
@@ -3514,7 +3435,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>13</v>
@@ -3536,7 +3457,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>13</v>
@@ -3558,7 +3479,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>13</v>
@@ -3580,7 +3501,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>13</v>
@@ -3605,13 +3526,13 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D147" s="6"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D148" s="6"/>
     </row>
@@ -3626,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>1</v>
@@ -3655,7 +3576,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>11</v>
@@ -3681,7 +3602,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>12</v>
@@ -3703,7 +3624,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>12</v>
@@ -3725,7 +3646,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>12</v>
@@ -3747,7 +3668,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>12</v>
@@ -3769,7 +3690,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>12</v>
@@ -3791,7 +3712,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>12</v>
@@ -3813,7 +3734,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>13</v>
@@ -3835,7 +3756,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>13</v>
@@ -3857,7 +3778,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>13</v>
@@ -3879,7 +3800,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>13</v>
@@ -3901,7 +3822,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>13</v>
@@ -3923,7 +3844,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>13</v>
@@ -3948,7 +3869,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D164" s="6"/>
     </row>
@@ -3963,7 +3884,7 @@
         <v>10</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>1</v>
@@ -3992,7 +3913,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>11</v>
@@ -4018,7 +3939,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>12</v>
@@ -4040,7 +3961,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>12</v>
@@ -4062,7 +3983,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>12</v>
@@ -4084,7 +4005,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>12</v>
@@ -4106,7 +4027,7 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>12</v>
@@ -4128,7 +4049,7 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>12</v>
@@ -4150,7 +4071,7 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>13</v>
@@ -4172,7 +4093,7 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>13</v>
@@ -4194,7 +4115,7 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>13</v>
@@ -4216,7 +4137,7 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>13</v>
@@ -4238,7 +4159,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>13</v>
@@ -4260,7 +4181,7 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>13</v>
@@ -4285,7 +4206,7 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D180" s="6"/>
     </row>
@@ -4300,7 +4221,7 @@
         <v>10</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>1</v>
@@ -4329,7 +4250,7 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>11</v>
@@ -4355,7 +4276,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>12</v>
@@ -4377,7 +4298,7 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>12</v>
@@ -4399,7 +4320,7 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>12</v>
@@ -4421,7 +4342,7 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B186" s="4" t="s">
         <v>12</v>
@@ -4443,7 +4364,7 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>12</v>
@@ -4465,7 +4386,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B188" s="4" t="s">
         <v>12</v>
@@ -4487,7 +4408,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>13</v>
@@ -4509,7 +4430,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B190" s="4" t="s">
         <v>13</v>
@@ -4531,7 +4452,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>13</v>
@@ -4553,7 +4474,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B192" s="4" t="s">
         <v>13</v>
@@ -4575,7 +4496,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>13</v>
@@ -4597,7 +4518,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B194" s="4" t="s">
         <v>13</v>
@@ -4622,7 +4543,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D196" s="6"/>
     </row>
@@ -4637,7 +4558,7 @@
         <v>10</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>1</v>
@@ -4666,7 +4587,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>11</v>
@@ -4692,7 +4613,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>12</v>
@@ -4714,7 +4635,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>12</v>
@@ -4736,7 +4657,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>12</v>
@@ -4758,7 +4679,7 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>12</v>
@@ -4780,7 +4701,7 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>12</v>
@@ -4802,7 +4723,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>12</v>
@@ -4824,7 +4745,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>13</v>
@@ -4846,7 +4767,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>13</v>
@@ -4868,7 +4789,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>13</v>
@@ -4890,7 +4811,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>13</v>
@@ -4912,7 +4833,7 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>13</v>
@@ -4934,7 +4855,7 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>13</v>
